--- a/config/Excel/Task.xlsx
+++ b/config/Excel/Task.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7805C9A5-DF28-4760-9993-F02F11679688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2401055-BF85-49B5-8941-1B3879167785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Task" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="232">
   <si>
     <t>順序</t>
   </si>
@@ -150,21 +150,6 @@
     <t>獨特(含)以上品質皆可</t>
   </si>
   <si>
-    <t>學習治療技能「再生術」</t>
-  </si>
-  <si>
-    <t>skillLevel</t>
-  </si>
-  <si>
-    <t>regenerate</t>
-  </si>
-  <si>
-    <t>skillXp</t>
-  </si>
-  <si>
-    <t>技能經驗值+10000</t>
-  </si>
-  <si>
     <t>強化裝備20次</t>
   </si>
   <si>
@@ -246,15 +231,6 @@
     <t>檢查身上同時鑲嵌的寶石數量</t>
   </si>
   <si>
-    <t>升級防禦技能「魔法屏障」至5級</t>
-  </si>
-  <si>
-    <t>manaBarrier</t>
-  </si>
-  <si>
-    <t>技能經驗值+50000</t>
-  </si>
-  <si>
     <t>生命最大值達5000</t>
   </si>
   <si>
@@ -360,9 +336,6 @@
     <t>maxHp＝生命最大值（屬性面板數值；掉回門檻以下進度也會掉）。目標參數留空。</t>
   </si>
   <si>
-    <t>skillLevel＝指定技能達到 N 級（N＝目標數量；1＝學會）。目標參數＝技能 id（查 Skills 表第一欄）。</t>
-  </si>
-  <si>
     <t>── 獎勵類型（與獎勵參數格式） ──</t>
   </si>
   <si>
@@ -710,6 +683,108 @@
   <si>
     <t>任意3太古史詩100級裝備×1</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>6. 2026-09-29 移除舊版技能系統：原「學習治療技能『再生術』」與「升級防禦技能『魔法屏障』至 5 級」兩個任務已刪除，skillLevel 目標類型不再存在；玩家存檔的領取進度已由存檔遷移（legacySkillRemovalV1）平移。</t>
   </si>
 </sst>
 </file>
@@ -780,19 +855,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1095,7 +1171,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1138,8 +1214,8 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
-        <v>149</v>
+      <c r="K1" s="2" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -1257,13 +1333,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="E6">
         <v>20</v>
@@ -1281,7 +1357,7 @@
         <v>33</v>
       </c>
       <c r="J6" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -1314,92 +1390,95 @@
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" s="3" t="s">
+        <v>198</v>
       </c>
       <c r="B8" t="s">
         <v>38</v>
       </c>
       <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8">
+        <v>20</v>
+      </c>
+      <c r="F8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8">
+        <v>500</v>
+      </c>
+      <c r="I8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" t="s">
+        <v>149</v>
+      </c>
+      <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" t="s">
+        <v>143</v>
+      </c>
+      <c r="E9">
+        <v>30</v>
+      </c>
+      <c r="F9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" t="s">
+        <v>123</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9" t="s">
+        <v>122</v>
+      </c>
+      <c r="J9" t="s">
         <v>39</v>
       </c>
-      <c r="D8" t="s">
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B10" t="s">
         <v>40</v>
       </c>
-      <c r="E8">
+      <c r="C10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10">
         <v>1</v>
       </c>
-      <c r="F8" t="s">
-        <v>41</v>
-      </c>
-      <c r="H8">
-        <v>10000</v>
-      </c>
-      <c r="I8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="H10">
+        <v>10</v>
+      </c>
+      <c r="I10" t="s">
         <v>43</v>
-      </c>
-      <c r="C9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9">
-        <v>20</v>
-      </c>
-      <c r="F9" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9">
-        <v>500</v>
-      </c>
-      <c r="I9" t="s">
-        <v>36</v>
-      </c>
-      <c r="J9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>158</v>
-      </c>
-      <c r="C10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" t="s">
-        <v>152</v>
-      </c>
-      <c r="E10">
-        <v>30</v>
-      </c>
-      <c r="F10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" t="s">
-        <v>132</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10" t="s">
-        <v>131</v>
       </c>
       <c r="J10" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="B11" t="s">
         <v>45</v>
@@ -1408,311 +1487,311 @@
         <v>46</v>
       </c>
       <c r="E11">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F11" t="s">
         <v>47</v>
       </c>
-      <c r="G11">
+      <c r="G11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11">
         <v>1</v>
       </c>
-      <c r="H11">
+      <c r="I11" t="s">
+        <v>49</v>
+      </c>
+      <c r="J11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12">
+        <v>4</v>
+      </c>
+      <c r="F12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12">
+        <v>50</v>
+      </c>
+      <c r="I12" t="s">
+        <v>53</v>
+      </c>
+      <c r="J12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B13" t="s">
+        <v>195</v>
+      </c>
+      <c r="C13" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
         <v>10</v>
       </c>
-      <c r="I11" t="s">
-        <v>48</v>
-      </c>
-      <c r="J11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12">
+      <c r="I13" t="s">
+        <v>43</v>
+      </c>
+      <c r="J13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B14" t="s">
+        <v>150</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" t="s">
+        <v>143</v>
+      </c>
+      <c r="E14">
+        <v>40</v>
+      </c>
+      <c r="F14" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" t="s">
+        <v>57</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14" t="s">
+        <v>58</v>
+      </c>
+      <c r="J14" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" t="s">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
+      <c r="D15" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15">
+        <v>4</v>
+      </c>
+      <c r="F15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15">
+        <v>500</v>
+      </c>
+      <c r="I15" t="s">
+        <v>36</v>
+      </c>
+      <c r="J15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16">
+        <v>16</v>
+      </c>
+      <c r="F16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>15</v>
+      </c>
+      <c r="I16" t="s">
+        <v>63</v>
+      </c>
+      <c r="J16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B17" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17">
+        <v>5000</v>
+      </c>
+      <c r="F17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17">
+        <v>300000</v>
+      </c>
+      <c r="I17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B18" t="s">
+        <v>151</v>
+      </c>
+      <c r="C18" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" t="s">
+        <v>143</v>
+      </c>
+      <c r="E18">
         <v>50</v>
       </c>
-      <c r="C12" t="s">
-        <v>51</v>
-      </c>
-      <c r="E12">
-        <v>2</v>
-      </c>
-      <c r="F12" t="s">
-        <v>52</v>
-      </c>
-      <c r="G12" t="s">
-        <v>53</v>
-      </c>
-      <c r="H12">
+      <c r="F18" t="s">
+        <v>31</v>
+      </c>
+      <c r="G18" t="s">
+        <v>68</v>
+      </c>
+      <c r="H18">
         <v>1</v>
       </c>
-      <c r="I12" t="s">
-        <v>54</v>
-      </c>
-      <c r="J12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13">
+      <c r="I18" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B19" t="s">
+        <v>181</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" t="s">
+        <v>70</v>
+      </c>
+      <c r="E19">
         <v>4</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F19" t="s">
         <v>27</v>
       </c>
-      <c r="H13">
-        <v>50</v>
-      </c>
-      <c r="I13" t="s">
-        <v>58</v>
-      </c>
-      <c r="J13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>204</v>
-      </c>
-      <c r="C14" t="s">
-        <v>60</v>
-      </c>
-      <c r="E14">
-        <v>2</v>
-      </c>
-      <c r="F14" t="s">
-        <v>47</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-      <c r="H14">
-        <v>10</v>
-      </c>
-      <c r="I14" t="s">
-        <v>48</v>
-      </c>
-      <c r="J14" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>159</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="H19">
+        <v>100</v>
+      </c>
+      <c r="I19" t="s">
+        <v>71</v>
+      </c>
+      <c r="J19" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B20" t="s">
+        <v>185</v>
+      </c>
+      <c r="C20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20">
         <v>30</v>
       </c>
-      <c r="D15" t="s">
-        <v>152</v>
-      </c>
-      <c r="E15">
-        <v>40</v>
-      </c>
-      <c r="F15" t="s">
-        <v>31</v>
-      </c>
-      <c r="G15" t="s">
-        <v>62</v>
-      </c>
-      <c r="H15">
-        <v>1</v>
-      </c>
-      <c r="I15" t="s">
-        <v>63</v>
-      </c>
-      <c r="J15" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" t="s">
-        <v>65</v>
-      </c>
-      <c r="E16">
-        <v>4</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="F20" t="s">
         <v>22</v>
       </c>
-      <c r="H16">
+      <c r="H20">
         <v>500</v>
       </c>
-      <c r="I16" t="s">
-        <v>36</v>
-      </c>
-      <c r="J16" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E17">
-        <v>16</v>
-      </c>
-      <c r="F17" t="s">
-        <v>47</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-      <c r="H17">
-        <v>15</v>
-      </c>
-      <c r="I17" t="s">
-        <v>68</v>
-      </c>
-      <c r="J17" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
-        <v>70</v>
-      </c>
-      <c r="C18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" t="s">
-        <v>71</v>
-      </c>
-      <c r="E18">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>41</v>
-      </c>
-      <c r="H18">
-        <v>50000</v>
-      </c>
-      <c r="I18" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" t="s">
-        <v>74</v>
-      </c>
-      <c r="E19">
-        <v>5000</v>
-      </c>
-      <c r="F19" t="s">
-        <v>13</v>
-      </c>
-      <c r="H19">
-        <v>300000</v>
-      </c>
-      <c r="I19" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>160</v>
-      </c>
-      <c r="C20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D20" t="s">
-        <v>152</v>
-      </c>
-      <c r="E20">
-        <v>50</v>
-      </c>
-      <c r="F20" t="s">
-        <v>31</v>
-      </c>
-      <c r="G20" t="s">
-        <v>76</v>
-      </c>
-      <c r="H20">
-        <v>1</v>
-      </c>
       <c r="I20" t="s">
-        <v>77</v>
+        <v>186</v>
+      </c>
+      <c r="J20" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" s="3" t="s">
+        <v>211</v>
       </c>
       <c r="B21" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C21" t="s">
         <v>11</v>
       </c>
       <c r="D21" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="E21">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F21" t="s">
         <v>27</v>
       </c>
       <c r="H21">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I21" t="s">
-        <v>79</v>
+        <v>125</v>
       </c>
       <c r="J21" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" s="3" t="s">
+        <v>212</v>
       </c>
       <c r="B22" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="C22" t="s">
         <v>21</v>
@@ -1727,47 +1806,47 @@
         <v>500</v>
       </c>
       <c r="I22" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="J22" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" s="3" t="s">
+        <v>213</v>
       </c>
       <c r="B23" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C23" t="s">
         <v>11</v>
       </c>
       <c r="D23" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="E23">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F23" t="s">
         <v>27</v>
       </c>
       <c r="H23">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="I23" t="s">
-        <v>134</v>
+        <v>184</v>
       </c>
       <c r="J23" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" s="3" t="s">
+        <v>214</v>
       </c>
       <c r="B24" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C24" t="s">
         <v>21</v>
@@ -1782,186 +1861,186 @@
         <v>500</v>
       </c>
       <c r="I24" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="J24" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" s="3" t="s">
+        <v>215</v>
       </c>
       <c r="B25" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C25" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25">
+        <v>10</v>
+      </c>
+      <c r="F25" t="s">
+        <v>42</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>40</v>
+      </c>
+      <c r="I25" t="s">
+        <v>189</v>
+      </c>
+      <c r="J25" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B26" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" t="s">
+        <v>74</v>
+      </c>
+      <c r="E26">
+        <v>6</v>
+      </c>
+      <c r="F26" t="s">
+        <v>27</v>
+      </c>
+      <c r="H26">
+        <v>200</v>
+      </c>
+      <c r="I26" t="s">
+        <v>125</v>
+      </c>
+      <c r="J26" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B27" t="s">
+        <v>152</v>
+      </c>
+      <c r="C27" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" t="s">
+        <v>143</v>
+      </c>
+      <c r="E27">
+        <v>100</v>
+      </c>
+      <c r="F27" t="s">
+        <v>31</v>
+      </c>
+      <c r="G27" t="s">
+        <v>196</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B28" t="s">
+        <v>190</v>
+      </c>
+      <c r="C28" t="s">
         <v>11</v>
       </c>
-      <c r="D25" t="s">
-        <v>78</v>
-      </c>
-      <c r="E25">
-        <v>13</v>
-      </c>
-      <c r="F25" t="s">
-        <v>27</v>
-      </c>
-      <c r="H25">
-        <v>400</v>
-      </c>
-      <c r="I25" t="s">
+      <c r="D28" t="s">
         <v>193</v>
       </c>
-      <c r="J25" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" t="s">
-        <v>196</v>
-      </c>
-      <c r="C26" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26">
-        <v>30</v>
-      </c>
-      <c r="F26" t="s">
-        <v>22</v>
-      </c>
-      <c r="H26">
-        <v>500</v>
-      </c>
-      <c r="I26" t="s">
-        <v>195</v>
-      </c>
-      <c r="J26" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27" t="s">
-        <v>197</v>
-      </c>
-      <c r="C27" t="s">
-        <v>46</v>
-      </c>
-      <c r="E27">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>47</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-      <c r="H27">
-        <v>40</v>
-      </c>
-      <c r="I27" t="s">
-        <v>198</v>
-      </c>
-      <c r="J27" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28" t="s">
-        <v>81</v>
-      </c>
-      <c r="C28" t="s">
-        <v>82</v>
-      </c>
       <c r="E28">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F28" t="s">
         <v>27</v>
       </c>
       <c r="H28">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I28" t="s">
-        <v>134</v>
+        <v>71</v>
       </c>
       <c r="J28" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" s="3" t="s">
+        <v>210</v>
       </c>
       <c r="B29" t="s">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="C29" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29">
         <v>30</v>
       </c>
-      <c r="D29" t="s">
-        <v>152</v>
-      </c>
-      <c r="E29">
-        <v>100</v>
-      </c>
       <c r="F29" t="s">
-        <v>31</v>
-      </c>
-      <c r="G29" t="s">
-        <v>205</v>
+        <v>22</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="I29" t="s">
-        <v>206</v>
+        <v>186</v>
+      </c>
+      <c r="J29" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>20</v>
+      <c r="A30" s="3" t="s">
+        <v>211</v>
       </c>
       <c r="B30" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="C30" t="s">
         <v>11</v>
       </c>
       <c r="D30" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F30" t="s">
         <v>27</v>
       </c>
       <c r="H30">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I30" t="s">
-        <v>79</v>
+        <v>125</v>
       </c>
       <c r="J30" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>21</v>
+      <c r="A31" s="3" t="s">
+        <v>212</v>
       </c>
       <c r="B31" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="C31" t="s">
         <v>21</v>
@@ -1976,47 +2055,47 @@
         <v>500</v>
       </c>
       <c r="I31" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="J31" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>22</v>
+      <c r="A32" s="3" t="s">
+        <v>213</v>
       </c>
       <c r="B32" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="C32" t="s">
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="E32">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F32" t="s">
         <v>27</v>
       </c>
       <c r="H32">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="I32" t="s">
-        <v>134</v>
+        <v>184</v>
       </c>
       <c r="J32" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>23</v>
+      <c r="A33" s="3" t="s">
+        <v>214</v>
       </c>
       <c r="B33" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C33" t="s">
         <v>21</v>
@@ -2031,247 +2110,247 @@
         <v>500</v>
       </c>
       <c r="I33" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="J33" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>24</v>
+      <c r="A34" s="3" t="s">
+        <v>215</v>
       </c>
       <c r="B34" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C34" t="s">
-        <v>11</v>
-      </c>
-      <c r="D34" t="s">
-        <v>202</v>
+        <v>41</v>
       </c>
       <c r="E34">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F34" t="s">
-        <v>27</v>
+        <v>42</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
       </c>
       <c r="H34">
-        <v>400</v>
+        <v>40</v>
       </c>
       <c r="I34" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="J34" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>25</v>
+      <c r="A35" s="3" t="s">
+        <v>216</v>
       </c>
       <c r="B35" t="s">
-        <v>196</v>
+        <v>124</v>
       </c>
       <c r="C35" t="s">
         <v>21</v>
       </c>
       <c r="E35">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F35" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H35">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="I35" t="s">
-        <v>195</v>
+        <v>126</v>
       </c>
       <c r="J35" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36">
+      <c r="A36" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B36" t="s">
+        <v>153</v>
+      </c>
+      <c r="C36" t="s">
+        <v>30</v>
+      </c>
+      <c r="D36" t="s">
+        <v>143</v>
+      </c>
+      <c r="E36">
+        <v>150</v>
+      </c>
+      <c r="F36" t="s">
+        <v>31</v>
+      </c>
+      <c r="G36" t="s">
+        <v>128</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36" t="s">
+        <v>127</v>
+      </c>
+      <c r="J36" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B37" t="s">
+        <v>129</v>
+      </c>
+      <c r="C37" t="s">
+        <v>141</v>
+      </c>
+      <c r="E37">
+        <v>5</v>
+      </c>
+      <c r="F37" t="s">
+        <v>42</v>
+      </c>
+      <c r="G37">
+        <v>2</v>
+      </c>
+      <c r="H37">
+        <v>15</v>
+      </c>
+      <c r="I37" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B38" t="s">
+        <v>131</v>
+      </c>
+      <c r="C38" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" t="s">
+        <v>132</v>
+      </c>
+      <c r="E38">
+        <v>13</v>
+      </c>
+      <c r="F38" t="s">
+        <v>22</v>
+      </c>
+      <c r="H38">
+        <v>50000</v>
+      </c>
+      <c r="I38" t="s">
+        <v>133</v>
+      </c>
+      <c r="J38" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B39" t="s">
+        <v>130</v>
+      </c>
+      <c r="C39" t="s">
         <v>26</v>
       </c>
-      <c r="B36" t="s">
-        <v>203</v>
-      </c>
-      <c r="C36" t="s">
-        <v>46</v>
-      </c>
-      <c r="E36">
-        <v>10</v>
-      </c>
-      <c r="F36" t="s">
-        <v>47</v>
-      </c>
-      <c r="G36">
+      <c r="E39">
+        <v>100</v>
+      </c>
+      <c r="F39" t="s">
+        <v>27</v>
+      </c>
+      <c r="H39">
+        <v>300</v>
+      </c>
+      <c r="I39" t="s">
+        <v>126</v>
+      </c>
+      <c r="J39" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B40" t="s">
+        <v>135</v>
+      </c>
+      <c r="C40" t="s">
+        <v>142</v>
+      </c>
+      <c r="E40">
+        <v>3</v>
+      </c>
+      <c r="F40" t="s">
+        <v>13</v>
+      </c>
+      <c r="H40">
+        <v>2000000</v>
+      </c>
+      <c r="I40" t="s">
+        <v>136</v>
+      </c>
+      <c r="J40" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B41" t="s">
+        <v>154</v>
+      </c>
+      <c r="C41" t="s">
+        <v>30</v>
+      </c>
+      <c r="D41" t="s">
+        <v>143</v>
+      </c>
+      <c r="E41">
+        <v>200</v>
+      </c>
+      <c r="F41" t="s">
+        <v>31</v>
+      </c>
+      <c r="G41" t="s">
+        <v>139</v>
+      </c>
+      <c r="H41">
         <v>1</v>
       </c>
-      <c r="H36">
-        <v>40</v>
-      </c>
-      <c r="I36" t="s">
-        <v>198</v>
-      </c>
-      <c r="J36" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>27</v>
-      </c>
-      <c r="B37" t="s">
-        <v>133</v>
-      </c>
-      <c r="C37" t="s">
-        <v>21</v>
-      </c>
-      <c r="E37">
-        <v>100</v>
-      </c>
-      <c r="F37" t="s">
-        <v>27</v>
-      </c>
-      <c r="H37">
-        <v>300</v>
-      </c>
-      <c r="I37" t="s">
-        <v>135</v>
-      </c>
-      <c r="J37" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>28</v>
-      </c>
-      <c r="B38" t="s">
-        <v>162</v>
-      </c>
-      <c r="C38" t="s">
-        <v>30</v>
-      </c>
-      <c r="D38" t="s">
-        <v>152</v>
-      </c>
-      <c r="E38">
-        <v>150</v>
-      </c>
-      <c r="F38" t="s">
-        <v>31</v>
-      </c>
-      <c r="G38" t="s">
-        <v>137</v>
-      </c>
-      <c r="H38">
-        <v>1</v>
-      </c>
-      <c r="I38" t="s">
-        <v>136</v>
-      </c>
-      <c r="J38" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>29</v>
-      </c>
-      <c r="B39" t="s">
+      <c r="I41" t="s">
         <v>138</v>
       </c>
-      <c r="C39" t="s">
-        <v>150</v>
-      </c>
-      <c r="E39">
-        <v>5</v>
-      </c>
-      <c r="F39" t="s">
-        <v>47</v>
-      </c>
-      <c r="G39">
-        <v>2</v>
-      </c>
-      <c r="H39">
-        <v>15</v>
-      </c>
-      <c r="I39" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>30</v>
-      </c>
-      <c r="B40" t="s">
-        <v>140</v>
-      </c>
-      <c r="C40" t="s">
-        <v>11</v>
-      </c>
-      <c r="D40" t="s">
-        <v>141</v>
-      </c>
-      <c r="E40">
-        <v>13</v>
-      </c>
-      <c r="F40" t="s">
-        <v>22</v>
-      </c>
-      <c r="H40">
-        <v>50000</v>
-      </c>
-      <c r="I40" t="s">
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B42" t="s">
+        <v>164</v>
+      </c>
+      <c r="C42" t="s">
         <v>142</v>
       </c>
-      <c r="J40" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>31</v>
-      </c>
-      <c r="B41" t="s">
-        <v>139</v>
-      </c>
-      <c r="C41" t="s">
-        <v>26</v>
-      </c>
-      <c r="E41">
-        <v>100</v>
-      </c>
-      <c r="F41" t="s">
-        <v>27</v>
-      </c>
-      <c r="H41">
-        <v>300</v>
-      </c>
-      <c r="I41" t="s">
-        <v>135</v>
-      </c>
-      <c r="J41" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>32</v>
-      </c>
-      <c r="B42" t="s">
-        <v>144</v>
-      </c>
-      <c r="C42" t="s">
-        <v>151</v>
-      </c>
       <c r="E42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F42" t="s">
         <v>13</v>
@@ -2280,239 +2359,184 @@
         <v>2000000</v>
       </c>
       <c r="I42" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="J42" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>33</v>
+      <c r="A43" s="3" t="s">
+        <v>224</v>
       </c>
       <c r="B43" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C43" t="s">
         <v>30</v>
       </c>
       <c r="D43" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="E43">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="F43" t="s">
         <v>31</v>
       </c>
       <c r="G43" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="H43">
         <v>1</v>
       </c>
       <c r="I43" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B44" t="s">
+        <v>158</v>
+      </c>
+      <c r="C44" t="s">
+        <v>30</v>
+      </c>
+      <c r="D44" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>34</v>
-      </c>
-      <c r="B44" t="s">
-        <v>173</v>
-      </c>
-      <c r="C44" t="s">
-        <v>151</v>
-      </c>
       <c r="E44">
-        <v>4</v>
+        <v>300</v>
       </c>
       <c r="F44" t="s">
-        <v>13</v>
+        <v>31</v>
+      </c>
+      <c r="G44" t="s">
+        <v>159</v>
       </c>
       <c r="H44">
-        <v>2000000</v>
+        <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>174</v>
-      </c>
-      <c r="J44" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>35</v>
+      <c r="A45" s="3" t="s">
+        <v>226</v>
       </c>
       <c r="B45" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="C45" t="s">
         <v>30</v>
       </c>
       <c r="D45" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E45">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="F45" t="s">
         <v>31</v>
       </c>
       <c r="G45" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="H45">
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>36</v>
+      <c r="A46" s="3" t="s">
+        <v>227</v>
       </c>
       <c r="B46" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C46" t="s">
         <v>30</v>
       </c>
       <c r="D46" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="E46">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="F46" t="s">
         <v>31</v>
       </c>
       <c r="G46" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="H46">
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>37</v>
+      <c r="A47" s="3" t="s">
+        <v>228</v>
       </c>
       <c r="B47" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C47" t="s">
         <v>30</v>
       </c>
       <c r="D47" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E47">
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="F47" t="s">
         <v>31</v>
       </c>
       <c r="G47" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="H47">
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>38</v>
+      <c r="A48" s="3" t="s">
+        <v>229</v>
       </c>
       <c r="B48" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="C48" t="s">
         <v>30</v>
       </c>
       <c r="D48" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="E48">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F48" t="s">
         <v>31</v>
       </c>
       <c r="G48" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="H48">
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>39</v>
-      </c>
-      <c r="B49" t="s">
-        <v>188</v>
-      </c>
-      <c r="C49" t="s">
-        <v>30</v>
-      </c>
-      <c r="D49" t="s">
-        <v>178</v>
-      </c>
-      <c r="E49">
-        <v>450</v>
-      </c>
-      <c r="F49" t="s">
-        <v>31</v>
-      </c>
-      <c r="G49" t="s">
-        <v>179</v>
-      </c>
-      <c r="H49">
-        <v>1</v>
-      </c>
-      <c r="I49" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>40</v>
-      </c>
-      <c r="B50" t="s">
-        <v>189</v>
-      </c>
-      <c r="C50" t="s">
-        <v>30</v>
-      </c>
-      <c r="D50" t="s">
-        <v>178</v>
-      </c>
-      <c r="E50">
-        <v>500</v>
-      </c>
-      <c r="F50" t="s">
-        <v>31</v>
-      </c>
-      <c r="G50" t="s">
-        <v>183</v>
-      </c>
-      <c r="H50">
-        <v>1</v>
-      </c>
-      <c r="I50" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -2526,283 +2550,297 @@
   <dimension ref="A1:A58"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="118" customWidth="1"/>
+    <col min="1" max="1" width="125.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
-    </row>
-    <row r="4" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+    <row r="13" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+    <row r="18" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3"/>
-    </row>
-    <row r="16" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+    <row r="32" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="5" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
+    <row r="39" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="3"/>
-    </row>
-    <row r="32" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="5" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
+    <row r="42" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A42" s="6" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
+    <row r="45" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A45" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="5" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="5" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
+    <row r="48" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A48" s="6" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
+    <row r="49" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A49" s="5" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="5" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="5" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
+    <row r="53" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A53" s="6" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="3"/>
-    </row>
-    <row r="42" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
+    <row r="54" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A54" s="5" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="5" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="3"/>
-    </row>
-    <row r="45" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A45" s="4" t="s">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="5" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="3"/>
-    </row>
-    <row r="48" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="s">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="5" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" s="3"/>
-    </row>
-    <row r="53" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A53" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" s="3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" s="3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" s="3" t="s">
-        <v>130</v>
+    <row r="58" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A58" s="5" t="s">
+        <v>231</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Task.xlsx
+++ b/config/Excel/Task.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2401055-BF85-49B5-8941-1B3879167785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8524337-AD52-4545-9E7A-F0F204B8BE19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="235">
   <si>
     <t>順序</t>
   </si>
@@ -171,24 +171,6 @@
     <t>檢查身上同時鑲嵌的寶石數量，拔下再裝不重複計數</t>
   </si>
   <si>
-    <t>裝備任意附魔2次</t>
-  </si>
-  <si>
-    <t>enchantCount</t>
-  </si>
-  <si>
-    <t>book</t>
-  </si>
-  <si>
-    <t>focus</t>
-  </si>
-  <si>
-    <t>專注附魔×1</t>
-  </si>
-  <si>
-    <t>累計附魔次數</t>
-  </si>
-  <si>
     <t>熔爐裝配任意零件4個</t>
   </si>
   <si>
@@ -318,9 +300,6 @@
     <t>rerollCount＝累計洗煉次數（整件洗與單條洗各計 1 次）。目標參數留空。</t>
   </si>
   <si>
-    <t>enchantCount＝累計附魔成功次數（被拒不計）。目標參數留空。</t>
-  </si>
-  <si>
     <t>composeCount＝累計寶石合成次數（「全部合成」一次合 N 組計 N）。目標參數留空。</t>
   </si>
   <si>
@@ -348,9 +327,6 @@
     <t>gem＝寶石（種類隨機）：獎勵參數＝寶石等級 1~5；獎勵數量＝顆數（每顆種類各自隨機）。</t>
   </si>
   <si>
-    <t>book＝附魔書：獎勵參數＝附魔書 id（見下方對照表）；獎勵數量＝本數。</t>
-  </si>
-  <si>
     <t>equip＝裝備：獎勵參數＝品質|等級|太古數；獎勵數量＝件數。</t>
   </si>
   <si>
@@ -785,6 +761,45 @@
   </si>
   <si>
     <t>6. 2026-09-29 移除舊版技能系統：原「學習治療技能『再生術』」與「升級防禦技能『魔法屏障』至 5 級」兩個任務已刪除，skillLevel 目標類型不再存在；玩家存檔的領取進度已由存檔遷移（legacySkillRemovalV1）平移。</t>
+  </si>
+  <si>
+    <t>在裝備上鑲嵌符文2次</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>runeSocketCount</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>rune</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>r02</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>餘燼符文×3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>累計鑲入符文次數（取代已關閉的附魔任務；符文在裝備頁「符文」鑲入）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enchantCount＝累計附魔成功次數（被拒不計）。目標參數留空。⚠️ 附魔功能已關閉（由符文取代），目前沒有任務使用此類型。</t>
+  </si>
+  <si>
+    <t>runeSocketCount＝累計鑲入符文的次數（成功才計；拆下再鑲會再計一次）。目標參數留空。</t>
+  </si>
+  <si>
+    <t>book＝附魔書：獎勵參數＝附魔書 id（見下方對照表）；獎勵數量＝本數。⚠️ 附魔功能已關閉，附魔書不再有用，請勿再當獎勵。</t>
+  </si>
+  <si>
+    <t>rune＝符文：獎勵參數＝符文 id（r01～r33，名稱與階數見 Runes 表）；獎勵數量＝顆數。</t>
   </si>
 </sst>
 </file>
@@ -855,7 +870,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -868,6 +883,9 @@
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1215,7 +1233,7 @@
         <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -1333,13 +1351,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="E6">
         <v>20</v>
@@ -1357,7 +1375,7 @@
         <v>33</v>
       </c>
       <c r="J6" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -1391,7 +1409,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="B8" t="s">
         <v>38</v>
@@ -1417,16 +1435,16 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="B9" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="C9" t="s">
         <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="E9">
         <v>30</v>
@@ -1435,13 +1453,13 @@
         <v>31</v>
       </c>
       <c r="G9" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="H9">
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="J9" t="s">
         <v>39</v>
@@ -1449,7 +1467,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="B10" t="s">
         <v>40</v>
@@ -1478,42 +1496,42 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="B11" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" t="s">
-        <v>46</v>
+        <v>193</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>225</v>
       </c>
       <c r="E11">
         <v>2</v>
       </c>
-      <c r="F11" t="s">
-        <v>47</v>
-      </c>
-      <c r="G11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-      <c r="I11" t="s">
-        <v>49</v>
-      </c>
-      <c r="J11" t="s">
-        <v>50</v>
+      <c r="F11" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E12">
         <v>4</v>
@@ -1525,21 +1543,21 @@
         <v>50</v>
       </c>
       <c r="I12" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="J12" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B13" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -1557,21 +1575,21 @@
         <v>43</v>
       </c>
       <c r="J13" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B14" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C14" t="s">
         <v>30</v>
       </c>
       <c r="D14" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="E14">
         <v>40</v>
@@ -1580,30 +1598,30 @@
         <v>31</v>
       </c>
       <c r="G14" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H14">
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="J14" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C15" t="s">
         <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E15">
         <v>4</v>
@@ -1618,15 +1636,15 @@
         <v>36</v>
       </c>
       <c r="J15" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="B16" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s">
         <v>41</v>
@@ -1644,21 +1662,21 @@
         <v>15</v>
       </c>
       <c r="I16" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="J16" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C17" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E17">
         <v>5000</v>
@@ -1670,21 +1688,21 @@
         <v>300000</v>
       </c>
       <c r="I17" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="B18" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="C18" t="s">
         <v>30</v>
       </c>
       <c r="D18" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="E18">
         <v>50</v>
@@ -1693,27 +1711,27 @@
         <v>31</v>
       </c>
       <c r="G18" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="H18">
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B19" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C19" t="s">
         <v>11</v>
       </c>
       <c r="D19" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E19">
         <v>4</v>
@@ -1725,18 +1743,18 @@
         <v>100</v>
       </c>
       <c r="I19" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="J19" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B20" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="C20" t="s">
         <v>21</v>
@@ -1751,7 +1769,7 @@
         <v>500</v>
       </c>
       <c r="I20" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="J20" t="s">
         <v>24</v>
@@ -1759,16 +1777,16 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B21" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="C21" t="s">
         <v>11</v>
       </c>
       <c r="D21" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E21">
         <v>8</v>
@@ -1780,18 +1798,18 @@
         <v>200</v>
       </c>
       <c r="I21" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="J21" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="B22" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="C22" t="s">
         <v>21</v>
@@ -1806,7 +1824,7 @@
         <v>500</v>
       </c>
       <c r="I22" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="J22" t="s">
         <v>24</v>
@@ -1814,16 +1832,16 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="B23" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C23" t="s">
         <v>11</v>
       </c>
       <c r="D23" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E23">
         <v>13</v>
@@ -1835,18 +1853,18 @@
         <v>400</v>
       </c>
       <c r="I23" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="J23" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="B24" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="C24" t="s">
         <v>21</v>
@@ -1861,7 +1879,7 @@
         <v>500</v>
       </c>
       <c r="I24" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="J24" t="s">
         <v>24</v>
@@ -1869,10 +1887,10 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B25" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="C25" t="s">
         <v>41</v>
@@ -1890,7 +1908,7 @@
         <v>40</v>
       </c>
       <c r="I25" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="J25" t="s">
         <v>44</v>
@@ -1898,13 +1916,13 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B26" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E26">
         <v>6</v>
@@ -1916,24 +1934,24 @@
         <v>200</v>
       </c>
       <c r="I26" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="J26" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B27" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="C27" t="s">
         <v>30</v>
       </c>
       <c r="D27" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="E27">
         <v>100</v>
@@ -1942,27 +1960,27 @@
         <v>31</v>
       </c>
       <c r="G27" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="H27">
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B28" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C28" t="s">
         <v>11</v>
       </c>
       <c r="D28" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="E28">
         <v>4</v>
@@ -1974,18 +1992,18 @@
         <v>100</v>
       </c>
       <c r="I28" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="J28" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B29" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="C29" t="s">
         <v>21</v>
@@ -2000,7 +2018,7 @@
         <v>500</v>
       </c>
       <c r="I29" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="J29" t="s">
         <v>24</v>
@@ -2008,16 +2026,16 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B30" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C30" t="s">
         <v>11</v>
       </c>
       <c r="D30" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -2029,18 +2047,18 @@
         <v>200</v>
       </c>
       <c r="I30" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="J30" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="B31" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="C31" t="s">
         <v>21</v>
@@ -2055,7 +2073,7 @@
         <v>500</v>
       </c>
       <c r="I31" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="J31" t="s">
         <v>24</v>
@@ -2063,16 +2081,16 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="B32" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C32" t="s">
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="E32">
         <v>13</v>
@@ -2084,18 +2102,18 @@
         <v>400</v>
       </c>
       <c r="I32" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="J32" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="B33" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="C33" t="s">
         <v>21</v>
@@ -2110,7 +2128,7 @@
         <v>500</v>
       </c>
       <c r="I33" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="J33" t="s">
         <v>24</v>
@@ -2118,10 +2136,10 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B34" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C34" t="s">
         <v>41</v>
@@ -2139,7 +2157,7 @@
         <v>40</v>
       </c>
       <c r="I34" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="J34" t="s">
         <v>44</v>
@@ -2147,10 +2165,10 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B35" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C35" t="s">
         <v>21</v>
@@ -2165,7 +2183,7 @@
         <v>300</v>
       </c>
       <c r="I35" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="J35" t="s">
         <v>24</v>
@@ -2173,16 +2191,16 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B36" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C36" t="s">
         <v>30</v>
       </c>
       <c r="D36" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="E36">
         <v>150</v>
@@ -2191,27 +2209,27 @@
         <v>31</v>
       </c>
       <c r="G36" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="H36">
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="J36" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="B37" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C37" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="E37">
         <v>5</v>
@@ -2226,21 +2244,21 @@
         <v>15</v>
       </c>
       <c r="I37" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="B38" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C38" t="s">
         <v>11</v>
       </c>
       <c r="D38" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="E38">
         <v>13</v>
@@ -2252,18 +2270,18 @@
         <v>50000</v>
       </c>
       <c r="I38" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="J38" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="B39" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C39" t="s">
         <v>26</v>
@@ -2278,7 +2296,7 @@
         <v>300</v>
       </c>
       <c r="I39" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="J39" t="s">
         <v>29</v>
@@ -2286,13 +2304,13 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="B40" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C40" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E40">
         <v>3</v>
@@ -2304,24 +2322,24 @@
         <v>2000000</v>
       </c>
       <c r="I40" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="J40" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="B41" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C41" t="s">
         <v>30</v>
       </c>
       <c r="D41" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="E41">
         <v>200</v>
@@ -2330,24 +2348,24 @@
         <v>31</v>
       </c>
       <c r="G41" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="H41">
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="B42" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C42" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E42">
         <v>4</v>
@@ -2359,24 +2377,24 @@
         <v>2000000</v>
       </c>
       <c r="I42" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="J42" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="B43" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C43" t="s">
         <v>30</v>
       </c>
       <c r="D43" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="E43">
         <v>250</v>
@@ -2385,27 +2403,27 @@
         <v>31</v>
       </c>
       <c r="G43" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H43">
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="B44" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="C44" t="s">
         <v>30</v>
       </c>
       <c r="D44" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="E44">
         <v>300</v>
@@ -2414,27 +2432,27 @@
         <v>31</v>
       </c>
       <c r="G44" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="H44">
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="B45" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C45" t="s">
         <v>30</v>
       </c>
       <c r="D45" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E45">
         <v>350</v>
@@ -2443,27 +2461,27 @@
         <v>31</v>
       </c>
       <c r="G45" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="H45">
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="B46" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C46" t="s">
         <v>30</v>
       </c>
       <c r="D46" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E46">
         <v>400</v>
@@ -2472,27 +2490,27 @@
         <v>31</v>
       </c>
       <c r="G46" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="H46">
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="B47" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="C47" t="s">
         <v>30</v>
       </c>
       <c r="D47" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="E47">
         <v>450</v>
@@ -2501,27 +2519,27 @@
         <v>31</v>
       </c>
       <c r="G47" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="H47">
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="B48" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="C48" t="s">
         <v>30</v>
       </c>
       <c r="D48" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="E48">
         <v>500</v>
@@ -2530,13 +2548,13 @@
         <v>31</v>
       </c>
       <c r="G48" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="H48">
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -2547,7 +2565,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:A58"/>
+  <dimension ref="A1:A60"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="125.7109375" customWidth="1"/>
@@ -2555,292 +2573,302 @@
   <sheetData>
     <row r="1" spans="1:1" ht="19.5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>94</v>
+        <v>231</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>95</v>
+        <v>232</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>144</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>145</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>230</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>100</v>
+        <v>222</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>105</v>
+        <v>233</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>106</v>
+        <v>234</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>110</v>
+        <v>222</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>230</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>163</v>
+        <v>222</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>112</v>
+        <v>155</v>
       </c>
     </row>
     <row r="48" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>230</v>
+        <v>106</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="53" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>231</v>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A60" s="7" t="s">
+        <v>223</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Task.xlsx
+++ b/config/Excel/Task.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alway\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8524337-AD52-4545-9E7A-F0F204B8BE19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E59F04FC-EBB3-4C2A-9D88-EE57A4047084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Task" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="239">
   <si>
     <t>順序</t>
   </si>
@@ -471,335 +471,361 @@
     <t>towerFloor＝高塔已通關的最高層數（N＝目標數量）。目標參數留空；層數與塔別無關（試煉/地獄/煉獄同一條層數軸）。</t>
   </si>
   <si>
+    <t>挑戰荒漠第50關BOSS成功</t>
+  </si>
+  <si>
+    <t>挑戰荒漠第100關BOSS成功</t>
+  </si>
+  <si>
+    <t>通關荒漠地圖第20關</t>
+  </si>
+  <si>
+    <t>通關荒漠地圖第40關</t>
+  </si>
+  <si>
+    <t>5|300|4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6|400|4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>任意4太古傳說300級裝備×1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>升級熔爐任意零件至4級</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>金幣+3000000</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>swamp</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>7|450|4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>任意4太古神話400級裝備×1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>任意4太古創世450級裝備×1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>任意4太古創世500級裝備×1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>7|500|4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>任意4太古傳說250級裝備×1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>5|250|4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6|350|4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>任意4太古神話350級裝備×1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>將4件裝備替換成50級史詩品質</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>將8件裝備替換成50級史詩品質</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>將13件裝備替換成50級史詩品質</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>附魔精華+400</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>強化裝備30次</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>裝備碎片+500</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>強化裝備40次</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>裝備鑲嵌任意寶石10顆</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>任意1級寶石×40</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>將4件裝備替換成100級史詩品質</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>將8件裝備替換成100級史詩品質</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>將13件裝備替換成100級史詩品質</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>4|100</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>裝備鑲嵌任意寶石20顆</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>合成寶石2次</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>4|100|3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>任意3太古史詩100級裝備×1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>6. 2026-09-29 移除舊版技能系統：原「學習治療技能『再生術』」與「升級防禦技能『魔法屏障』至 5 級」兩個任務已刪除，skillLevel 目標類型不再存在；玩家存檔的領取進度已由存檔遷移（legacySkillRemovalV1）平移。</t>
+  </si>
+  <si>
+    <t>在裝備上鑲嵌符文2次</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>runeSocketCount</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>rune</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>r02</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>餘燼符文×3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>累計鑲入符文次數（取代已關閉的附魔任務；符文在裝備頁「符文」鑲入）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enchantCount＝累計附魔成功次數（被拒不計）。目標參數留空。⚠️ 附魔功能已關閉（由符文取代），目前沒有任務使用此類型。</t>
+  </si>
+  <si>
+    <t>runeSocketCount＝累計鑲入符文的次數（成功才計；拆下再鑲會再計一次）。目標參數留空。</t>
+  </si>
+  <si>
+    <t>book＝附魔書：獎勵參數＝附魔書 id（見下方對照表）；獎勵數量＝本數。⚠️ 附魔功能已關閉，附魔書不再有用，請勿再當獎勵。</t>
+  </si>
+  <si>
+    <t>rune＝符文：獎勵參數＝符文 id（r01～r33，名稱與階數見 Runes 表）；獎勵數量＝顆數。</t>
+  </si>
+  <si>
+    <t>挑戰冰原第150關BOSS成功</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>Icefield</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>挑戰迷霧森林第200關BOSS成功</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>mist_forest</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>挑戰熔岩山第250關BOSS成功</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>lava_mountain</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>挑戰月影沼澤第300關BOSS成功</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>挑戰落雷峰第350關BOSS成功</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>thunder_peak</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>挑戰亡靈山脈第400關BOSS成功</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>undead_mountains</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>挑戰太古戰場第450關BOSS成功</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>god_battlefield</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>挑戰混沌界第500關BOSS成功</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>god_chaos</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>挑戰荒漠第20關成功</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>挑戰荒漠第30關成功</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>挑戰荒漠第40關成功</t>
-  </si>
-  <si>
-    <t>挑戰荒漠第50關BOSS成功</t>
-  </si>
-  <si>
-    <t>挑戰荒漠第100關BOSS成功</t>
-  </si>
-  <si>
-    <t>挑戰荒漠第150關BOSS成功</t>
-  </si>
-  <si>
-    <t>挑戰荒漠第200關BOSS成功</t>
-  </si>
-  <si>
-    <t>通關荒漠地圖第20關</t>
-  </si>
-  <si>
-    <t>通關荒漠地圖第40關</t>
-  </si>
-  <si>
-    <t>swamp</t>
-  </si>
-  <si>
-    <t>挑戰冰原第300關BOSS成功</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>5|300|4</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>6|400|4</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>任意4太古傳說300級裝備×1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>挑戰沼澤第400關BOSS成功</t>
-  </si>
-  <si>
-    <t>desert＝荒漠、Icefield＝冰原、swamp＝沼澤、undead_mountains＝亡靈山脈、god_battlefield＝太古戰場、god_chaos＝混沌界、god_sanctuary＝永恒神域</t>
-  </si>
-  <si>
-    <t>升級熔爐任意零件至4級</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>金幣+3000000</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>挑戰冰原第250關BOSS成功</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>挑戰沼澤第350關BOSS成功</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>swamp</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>undead_mountains</t>
-  </si>
-  <si>
-    <t>7|450|4</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>任意4太古神話400級裝備×1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>任意4太古創世450級裝備×1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>任意4太古創世500級裝備×1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>7|500|4</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>任意4太古傳說250級裝備×1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>5|250|4</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>6|350|4</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>任意4太古神話350級裝備×1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>挑戰亡靈山脈第450關BOSS成功</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>挑戰亡靈山脈第500關BOSS成功</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>將4件裝備替換成50級史詩品質</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>將8件裝備替換成50級史詩品質</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>將13件裝備替換成50級史詩品質</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>附魔精華+400</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>強化裝備30次</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>裝備碎片+500</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>強化裝備40次</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>裝備鑲嵌任意寶石10顆</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>任意1級寶石×40</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>將4件裝備替換成100級史詩品質</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>將8件裝備替換成100級史詩品質</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>將13件裝備替換成100級史詩品質</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>4|100</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>裝備鑲嵌任意寶石20顆</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>合成寶石2次</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>4|100|3</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>任意3太古史詩100級裝備×1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>6. 2026-09-29 移除舊版技能系統：原「學習治療技能『再生術』」與「升級防禦技能『魔法屏障』至 5 級」兩個任務已刪除，skillLevel 目標類型不再存在；玩家存檔的領取進度已由存檔遷移（legacySkillRemovalV1）平移。</t>
-  </si>
-  <si>
-    <t>在裝備上鑲嵌符文2次</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>runeSocketCount</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>rune</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>r02</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>餘燼符文×3</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>累計鑲入符文次數（取代已關閉的附魔任務；符文在裝備頁「符文」鑲入）</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>enchantCount＝累計附魔成功次數（被拒不計）。目標參數留空。⚠️ 附魔功能已關閉（由符文取代），目前沒有任務使用此類型。</t>
-  </si>
-  <si>
-    <t>runeSocketCount＝累計鑲入符文的次數（成功才計；拆下再鑲會再計一次）。目標參數留空。</t>
-  </si>
-  <si>
-    <t>book＝附魔書：獎勵參數＝附魔書 id（見下方對照表）；獎勵數量＝本數。⚠️ 附魔功能已關閉，附魔書不再有用，請勿再當獎勵。</t>
-  </si>
-  <si>
-    <t>rune＝符文：獎勵參數＝符文 id（r01～r33，名稱與階數見 Runes 表）；獎勵數量＝顆數。</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>desert＝荒漠、Icefield＝冰原、mist_forest＝迷霧森林、lava_mountain＝熔岩山、swamp＝月影沼澤、thunder_peak＝落雷峰、undead_mountains＝亡靈山脈、god_battlefield＝太古戰場、god_chaos＝混沌界、god_sanctuary＝永恒神域</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1190,7 +1216,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K48"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -1201,7 +1227,7 @@
     <col min="10" max="10" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1236,7 +1262,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1265,7 +1291,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1294,7 +1320,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1320,7 +1346,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1346,12 +1372,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>140</v>
+      <c r="B6" s="3" t="s">
+        <v>235</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
@@ -1375,10 +1401,10 @@
         <v>33</v>
       </c>
       <c r="J6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1407,9 +1433,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="B8" t="s">
         <v>38</v>
@@ -1433,12 +1459,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="B9" t="s">
-        <v>141</v>
+        <v>176</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>236</v>
       </c>
       <c r="C9" t="s">
         <v>30</v>
@@ -1465,9 +1491,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="B10" t="s">
         <v>40</v>
@@ -1494,38 +1520,38 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="E11">
         <v>2</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="B12" t="s">
         <v>45</v>
@@ -1549,12 +1575,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="B13" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="C13" t="s">
         <v>49</v>
@@ -1578,12 +1604,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="B14" t="s">
-        <v>142</v>
+        <v>181</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>237</v>
       </c>
       <c r="C14" t="s">
         <v>30</v>
@@ -1607,12 +1633,12 @@
         <v>52</v>
       </c>
       <c r="J14" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="B15" t="s">
         <v>53</v>
@@ -1639,9 +1665,9 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s">
         <v>56</v>
@@ -1668,9 +1694,9 @@
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s">
         <v>59</v>
@@ -1691,12 +1717,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="B18" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C18" t="s">
         <v>30</v>
@@ -1720,12 +1746,12 @@
         <v>63</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="B19" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="C19" t="s">
         <v>11</v>
@@ -1749,12 +1775,12 @@
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="B20" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="C20" t="s">
         <v>21</v>
@@ -1769,18 +1795,18 @@
         <v>500</v>
       </c>
       <c r="I20" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="J20" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="B21" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="C21" t="s">
         <v>11</v>
@@ -1804,12 +1830,12 @@
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="B22" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="C22" t="s">
         <v>21</v>
@@ -1824,18 +1850,18 @@
         <v>500</v>
       </c>
       <c r="I22" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="J22" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="B23" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="C23" t="s">
         <v>11</v>
@@ -1853,18 +1879,18 @@
         <v>400</v>
       </c>
       <c r="I23" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="J23" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="B24" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="C24" t="s">
         <v>21</v>
@@ -1879,18 +1905,18 @@
         <v>500</v>
       </c>
       <c r="I24" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="J24" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="B25" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="C25" t="s">
         <v>41</v>
@@ -1908,15 +1934,15 @@
         <v>40</v>
       </c>
       <c r="I25" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="J25" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="B26" t="s">
         <v>67</v>
@@ -1940,12 +1966,12 @@
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="B27" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C27" t="s">
         <v>30</v>
@@ -1960,27 +1986,27 @@
         <v>31</v>
       </c>
       <c r="G27" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="H27">
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="B28" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="C28" t="s">
         <v>11</v>
       </c>
       <c r="D28" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="E28">
         <v>4</v>
@@ -1998,12 +2024,12 @@
         <v>66</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="B29" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="C29" t="s">
         <v>21</v>
@@ -2018,24 +2044,24 @@
         <v>500</v>
       </c>
       <c r="I29" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="J29" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="B30" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="C30" t="s">
         <v>11</v>
       </c>
       <c r="D30" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -2053,12 +2079,12 @@
         <v>66</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="B31" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="C31" t="s">
         <v>21</v>
@@ -2073,24 +2099,24 @@
         <v>500</v>
       </c>
       <c r="I31" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="J31" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="B32" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="C32" t="s">
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="E32">
         <v>13</v>
@@ -2102,18 +2128,18 @@
         <v>400</v>
       </c>
       <c r="I32" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="J32" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="B33" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="C33" t="s">
         <v>21</v>
@@ -2128,18 +2154,18 @@
         <v>500</v>
       </c>
       <c r="I33" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="J33" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="B34" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="C34" t="s">
         <v>41</v>
@@ -2157,15 +2183,15 @@
         <v>40</v>
       </c>
       <c r="I34" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="J34" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="B35" t="s">
         <v>116</v>
@@ -2189,18 +2215,18 @@
         <v>24</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="B36" t="s">
-        <v>145</v>
+        <v>194</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>220</v>
       </c>
       <c r="C36" t="s">
         <v>30</v>
       </c>
-      <c r="D36" t="s">
-        <v>135</v>
+      <c r="D36" s="3" t="s">
+        <v>221</v>
       </c>
       <c r="E36">
         <v>150</v>
@@ -2217,13 +2243,13 @@
       <c r="I36" t="s">
         <v>119</v>
       </c>
-      <c r="J36" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J36" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="B37" t="s">
         <v>121</v>
@@ -2247,9 +2273,9 @@
         <v>129</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="B38" t="s">
         <v>123</v>
@@ -2276,9 +2302,9 @@
         <v>66</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="B39" t="s">
         <v>122</v>
@@ -2302,9 +2328,9 @@
         <v>29</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="B40" t="s">
         <v>127</v>
@@ -2328,18 +2354,18 @@
         <v>126</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="B41" t="s">
-        <v>146</v>
+        <v>199</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>222</v>
       </c>
       <c r="C41" t="s">
         <v>30</v>
       </c>
-      <c r="D41" t="s">
-        <v>135</v>
+      <c r="D41" s="3" t="s">
+        <v>223</v>
       </c>
       <c r="E41">
         <v>200</v>
@@ -2357,12 +2383,12 @@
         <v>130</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="B42" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="C42" t="s">
         <v>134</v>
@@ -2377,24 +2403,24 @@
         <v>2000000</v>
       </c>
       <c r="I42" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="J42" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="B43" t="s">
-        <v>158</v>
+        <v>201</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>224</v>
       </c>
       <c r="C43" t="s">
         <v>30</v>
       </c>
-      <c r="D43" t="s">
-        <v>139</v>
+      <c r="D43" s="3" t="s">
+        <v>225</v>
       </c>
       <c r="E43">
         <v>250</v>
@@ -2403,27 +2429,27 @@
         <v>31</v>
       </c>
       <c r="G43" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="H43">
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="B44" t="s">
-        <v>150</v>
+        <v>202</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>226</v>
       </c>
       <c r="C44" t="s">
         <v>30</v>
       </c>
-      <c r="D44" t="s">
-        <v>139</v>
+      <c r="D44" s="3" t="s">
+        <v>148</v>
       </c>
       <c r="E44">
         <v>300</v>
@@ -2432,27 +2458,27 @@
         <v>31</v>
       </c>
       <c r="G44" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="H44">
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B45" t="s">
-        <v>159</v>
+        <v>203</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>227</v>
       </c>
       <c r="C45" t="s">
         <v>30</v>
       </c>
-      <c r="D45" t="s">
-        <v>149</v>
+      <c r="D45" s="3" t="s">
+        <v>228</v>
       </c>
       <c r="E45">
         <v>350</v>
@@ -2461,27 +2487,27 @@
         <v>31</v>
       </c>
       <c r="G45" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="H45">
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B46" t="s">
-        <v>154</v>
+        <v>204</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>229</v>
       </c>
       <c r="C46" t="s">
         <v>30</v>
       </c>
-      <c r="D46" t="s">
-        <v>160</v>
+      <c r="D46" s="3" t="s">
+        <v>230</v>
       </c>
       <c r="E46">
         <v>400</v>
@@ -2490,27 +2516,27 @@
         <v>31</v>
       </c>
       <c r="G46" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H46">
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B47" t="s">
-        <v>171</v>
+        <v>205</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>231</v>
       </c>
       <c r="C47" t="s">
         <v>30</v>
       </c>
-      <c r="D47" t="s">
-        <v>161</v>
+      <c r="D47" s="3" t="s">
+        <v>232</v>
       </c>
       <c r="E47">
         <v>450</v>
@@ -2519,27 +2545,27 @@
         <v>31</v>
       </c>
       <c r="G47" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="H47">
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="B48" t="s">
-        <v>172</v>
+        <v>206</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>233</v>
       </c>
       <c r="C48" t="s">
         <v>30</v>
       </c>
-      <c r="D48" t="s">
-        <v>161</v>
+      <c r="D48" s="3" t="s">
+        <v>234</v>
       </c>
       <c r="E48">
         <v>500</v>
@@ -2548,13 +2574,13 @@
         <v>31</v>
       </c>
       <c r="G48" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="H48">
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -2566,309 +2592,309 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A60"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="125.7109375" customWidth="1"/>
+    <col min="1" max="1" width="125.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="19.8" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" ht="30" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" ht="30" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" ht="30" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" ht="30" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" ht="30" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" ht="30" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" ht="30" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="41" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" ht="30" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="45" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="47" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" ht="30" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="51" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1" ht="30" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1" ht="30" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="53" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="56" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1" ht="30" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" s="7" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="60" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:1" ht="30" x14ac:dyDescent="0.3">
       <c r="A60" s="7" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Task.xlsx
+++ b/config/Excel/Task.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alway\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E59F04FC-EBB3-4C2A-9D88-EE57A4047084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7148595B-0694-47CF-84FE-3D0B135F05D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -824,7 +824,7 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>desert＝荒漠、Icefield＝冰原、mist_forest＝迷霧森林、lava_mountain＝熔岩山、swamp＝月影沼澤、thunder_peak＝落雷峰、undead_mountains＝亡靈山脈、god_battlefield＝太古戰場、god_chaos＝混沌界、god_sanctuary＝永恒神域</t>
+    <t>desert＝荒漠、Icefield＝冰原、mist_forest＝迷霧森林、lava_mountain＝熔岩山、swamp＝月影沼澤、thunder_peak＝落雷峰、undead_mountains＝亡靈山脈、god_battlefield＝太古戰場、god_chaos＝混沌界、god_sanctuary＝永恒神殿</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
